--- a/public/exports-60-250/70960516.xlsx
+++ b/public/exports-60-250/70960516.xlsx
@@ -1016,26 +1016,26 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionalle 8</t>
+          <t xml:space="preserve">Stampevej 10</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2960</t>
+          <t xml:space="preserve">2970</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2381978</t>
+          <t xml:space="preserve">2370057</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J14">
-        <v>200</v>
+        <v>82</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1091,17 +1091,17 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stampevej 10</t>
+          <t xml:space="preserve">Ulvemosen 7</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2970</t>
+          <t xml:space="preserve">2960</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2370057</t>
+          <t xml:space="preserve">2366592</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="J15">
-        <v>82</v>
+        <v>205</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1166,26 +1166,26 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ulvemosen 7</t>
+          <t xml:space="preserve">Ådalsparkvej 4A</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2960</t>
+          <t xml:space="preserve">2970</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2366592</t>
+          <t xml:space="preserve">2369282</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J16">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ådalsparkvej 4A</t>
+          <t xml:space="preserve">Lundevej 24</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1251,40 +1251,40 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2369282</t>
+          <t xml:space="preserve">9990363</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J17">
-        <v>196</v>
+        <v>112</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311265098</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Danakon a/s</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2027-08-09</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -1316,17 +1316,17 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundevej 24</t>
+          <t xml:space="preserve">Stadionalle 5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2970</t>
+          <t xml:space="preserve">2960</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">9990363</t>
+          <t xml:space="preserve">9153682</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1335,11 +1335,11 @@
         </is>
       </c>
       <c r="J18">
-        <v>112</v>
+        <v>176</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265098</t>
+          <t xml:space="preserve">311265099</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1406,15 +1406,15 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J19">
-        <v>176</v>
+        <v>127</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265099</t>
+          <t xml:space="preserve">311265093</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1466,30 +1466,30 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionalle 5</t>
+          <t xml:space="preserve">Bloustrødvej 11A</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2960</t>
+          <t xml:space="preserve">2970</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">9153682</t>
+          <t xml:space="preserve">2369496</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J20">
-        <v>127</v>
+        <v>162</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265093</t>
+          <t xml:space="preserve">311265958</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-09</t>
+          <t xml:space="preserve">2027-08-14</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bloustrødvej 11A</t>
+          <t xml:space="preserve">Bloustrødvej 13B</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2369496</t>
+          <t xml:space="preserve">7853948</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1560,11 +1560,11 @@
         </is>
       </c>
       <c r="J21">
-        <v>162</v>
+        <v>86</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265958</t>
+          <t xml:space="preserve">311336533</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bloustrødvej 13B</t>
+          <t xml:space="preserve">Bloustrødvej 15A</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">7853948</t>
+          <t xml:space="preserve">2369498</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t xml:space="preserve">311336533</t>
+          <t xml:space="preserve">311265956</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bloustrødvej 15A</t>
+          <t xml:space="preserve">Bloustrødvej 1A</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2369498</t>
+          <t xml:space="preserve">9072790</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1710,11 +1710,11 @@
         </is>
       </c>
       <c r="J23">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265956</t>
+          <t xml:space="preserve">311265960</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bloustrødvej 1A</t>
+          <t xml:space="preserve">Bloustrødvej 1B</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">9072790</t>
+          <t xml:space="preserve">2369491</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1785,11 +1785,11 @@
         </is>
       </c>
       <c r="J24">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265960</t>
+          <t xml:space="preserve">311265961</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bloustrødvej 1B</t>
+          <t xml:space="preserve">Bloustrødvej 21B</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2369491</t>
+          <t xml:space="preserve">2369539</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1860,11 +1860,11 @@
         </is>
       </c>
       <c r="J25">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265961</t>
+          <t xml:space="preserve">311265967</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bloustrødvej 21B</t>
+          <t xml:space="preserve">Bloustrødvej 23A</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2369539</t>
+          <t xml:space="preserve">7632534</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265967</t>
+          <t xml:space="preserve">311265968</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bloustrødvej 23A</t>
+          <t xml:space="preserve">Bloustrødvej 25B</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">7632534</t>
+          <t xml:space="preserve">8287549</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2010,11 +2010,11 @@
         </is>
       </c>
       <c r="J27">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265968</t>
+          <t xml:space="preserve">311265969</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bloustrødvej 25B</t>
+          <t xml:space="preserve">Bloustrødvej 27A</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">8287549</t>
+          <t xml:space="preserve">2369536</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265969</t>
+          <t xml:space="preserve">311265970</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bloustrødvej 27A</t>
+          <t xml:space="preserve">Bloustrødvej 29A</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2369536</t>
+          <t xml:space="preserve">7815341</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2160,11 +2160,11 @@
         </is>
       </c>
       <c r="J29">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265970</t>
+          <t xml:space="preserve">311265972</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bloustrødvej 29A</t>
+          <t xml:space="preserve">Bloustrødvej 3B</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">7815341</t>
+          <t xml:space="preserve">7968240</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2235,11 +2235,11 @@
         </is>
       </c>
       <c r="J30">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265972</t>
+          <t xml:space="preserve">311265962</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bloustrødvej 3B</t>
+          <t xml:space="preserve">Bloustrødvej 9A</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">7968240</t>
+          <t xml:space="preserve">7632535</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2310,11 +2310,11 @@
         </is>
       </c>
       <c r="J31">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265962</t>
+          <t xml:space="preserve">311265966</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bloustrødvej 9A</t>
+          <t xml:space="preserve">Stampevej 5</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">7632535</t>
+          <t xml:space="preserve">2369502</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2385,11 +2385,11 @@
         </is>
       </c>
       <c r="J32">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265966</t>
+          <t xml:space="preserve">311265976</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stampevej 5</t>
+          <t xml:space="preserve">Stampevej 7</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2369502</t>
+          <t xml:space="preserve">2369501</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265976</t>
+          <t xml:space="preserve">311337847</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stampevej 7</t>
+          <t xml:space="preserve">Sdr. Jagtvej 10</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2526,20 +2526,20 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2369501</t>
+          <t xml:space="preserve">2367182</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J34">
-        <v>86</v>
+        <v>203</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t xml:space="preserve">311337847</t>
+          <t xml:space="preserve">311269865</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-14</t>
+          <t xml:space="preserve">2027-08-31</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sdr. Jagtvej 10</t>
+          <t xml:space="preserve">Lundevej 18</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2601,20 +2601,20 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2367182</t>
+          <t xml:space="preserve">9990363</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J35">
-        <v>203</v>
+        <v>88</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t xml:space="preserve">311269865</t>
+          <t xml:space="preserve">311272831</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-31</t>
+          <t xml:space="preserve">2027-09-14</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundevej 18</t>
+          <t xml:space="preserve">Lundevej 20</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J36">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundevej 20</t>
+          <t xml:space="preserve">Kokkedal Alle 1</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2751,20 +2751,20 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">9990363</t>
+          <t xml:space="preserve">9761663</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J37">
-        <v>88</v>
+        <v>169</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t xml:space="preserve">311272831</t>
+          <t xml:space="preserve">311279820</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-14</t>
+          <t xml:space="preserve">2027-10-23</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kokkedal Alle 1</t>
+          <t xml:space="preserve">Ved Møllen 10</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">9761663</t>
+          <t xml:space="preserve">2367436</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2835,11 +2835,11 @@
         </is>
       </c>
       <c r="J38">
-        <v>169</v>
+        <v>140</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t xml:space="preserve">311279820</t>
+          <t xml:space="preserve">311289218</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-23</t>
+          <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -2891,30 +2891,30 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionalle 10</t>
+          <t xml:space="preserve">Ved Møllen 10</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2960</t>
+          <t xml:space="preserve">2970</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2381978</t>
+          <t xml:space="preserve">2367436</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J39">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286266</t>
+          <t xml:space="preserve">311289219</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-29</t>
+          <t xml:space="preserve">2027-12-18</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -2966,30 +2966,30 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionalle 8</t>
+          <t xml:space="preserve">Stampevej 10</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2960</t>
+          <t xml:space="preserve">2970</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2381978</t>
+          <t xml:space="preserve">2370057</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J40">
-        <v>140</v>
+        <v>240</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286267</t>
+          <t xml:space="preserve">311291492</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2999,7 +2999,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-29</t>
+          <t xml:space="preserve">2028-01-08</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3041,30 +3041,30 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Møllen 10</t>
+          <t xml:space="preserve">Østre Stationsvej 1A</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2970</t>
+          <t xml:space="preserve">2960</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2367436</t>
+          <t xml:space="preserve">2380704</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J41">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289218</t>
+          <t xml:space="preserve">311306142</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3074,7 +3074,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-18</t>
+          <t xml:space="preserve">2028-04-03</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3116,30 +3116,30 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Møllen 10</t>
+          <t xml:space="preserve">Østre Stationsvej 1A</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2970</t>
+          <t xml:space="preserve">2960</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2367436</t>
+          <t xml:space="preserve">2380704</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J42">
-        <v>166</v>
+        <v>95</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289219</t>
+          <t xml:space="preserve">311306140</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-18</t>
+          <t xml:space="preserve">2028-04-03</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stampevej 10</t>
+          <t xml:space="preserve">Gl Byvej 10</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3201,30 +3201,30 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2370057</t>
+          <t xml:space="preserve">7966206</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J43">
-        <v>240</v>
+        <v>156</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291492</t>
+          <t xml:space="preserve">311916600</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Danakon a/s</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-08</t>
+          <t xml:space="preserve">2036-07-30</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3266,40 +3266,40 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Stationsvej 1A</t>
+          <t xml:space="preserve">Sdr. Jagtvej 2</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2960</t>
+          <t xml:space="preserve">2970</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2380704</t>
+          <t xml:space="preserve">2367273</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J44">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311306142</t>
+          <t xml:space="preserve">311923296</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Danakon a/s</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-03</t>
+          <t xml:space="preserve">2036-09-02</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Stationsvej 1A</t>
+          <t xml:space="preserve">Stadionalle 10</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3351,30 +3351,30 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2380704</t>
+          <t xml:space="preserve">2381978</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J45">
-        <v>95</v>
+        <v>186</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311306140</t>
+          <t xml:space="preserve">311931619</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Danakon a/s</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-03</t>
+          <t xml:space="preserve">2036-10-13</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3416,30 +3416,30 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Byvej 10</t>
+          <t xml:space="preserve">Stadionalle 8</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2970</t>
+          <t xml:space="preserve">2960</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">7966206</t>
+          <t xml:space="preserve">2381978</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J46">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311916600</t>
+          <t xml:space="preserve">311931619</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-30</t>
+          <t xml:space="preserve">2036-10-13</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3491,30 +3491,30 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sdr. Jagtvej 2</t>
+          <t xml:space="preserve">Stadionalle 8</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2970</t>
+          <t xml:space="preserve">2960</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2367273</t>
+          <t xml:space="preserve">2381978</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J47">
-        <v>163</v>
+        <v>200</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311923296</t>
+          <t xml:space="preserve">311931619</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-02</t>
+          <t xml:space="preserve">2036-10-13</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
